--- a/backend/src/tmp/cotizacion.xlsx
+++ b/backend/src/tmp/cotizacion.xlsx
@@ -17,81 +17,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>CLIENTE:</t>
   </si>
   <si>
+    <t>Bodega c.a</t>
+  </si>
+  <si>
+    <t>Por favor hacer referencia en su orden de compra</t>
+  </si>
+  <si>
+    <t>Cotización Nº:</t>
+  </si>
+  <si>
+    <t>Fecha:</t>
+  </si>
+  <si>
+    <t>C.I Y RIF :</t>
+  </si>
+  <si>
+    <t>28739420</t>
+  </si>
+  <si>
+    <t>26-001-M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t>Validez de Oferta:</t>
+  </si>
+  <si>
+    <t>Condición de pago</t>
+  </si>
+  <si>
+    <t>TELÉFONO:</t>
+  </si>
+  <si>
+    <t>04124381354</t>
+  </si>
+  <si>
+    <t>5 dias</t>
+  </si>
+  <si>
+    <t>efectivo</t>
+  </si>
+  <si>
+    <t>Ciudad bolivar</t>
+  </si>
+  <si>
+    <t>Persona de Cont:</t>
+  </si>
+  <si>
+    <t>Nº Directo:</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN:</t>
+  </si>
+  <si>
+    <t>Joseph Martinez</t>
+  </si>
+  <si>
+    <t>04161235456</t>
+  </si>
+  <si>
+    <t>ATENCIÓN:</t>
+  </si>
+  <si>
     <t>Joseph</t>
   </si>
   <si>
-    <t>Por favor hacer referencia en su orden de compra</t>
-  </si>
-  <si>
-    <t>Cotización Nº:</t>
-  </si>
-  <si>
-    <t>Fecha:</t>
-  </si>
-  <si>
-    <t>C.I Y RIF :</t>
-  </si>
-  <si>
-    <t>28788745</t>
-  </si>
-  <si>
-    <t>2533</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
-  </si>
-  <si>
-    <t>Validez de Oferta:</t>
-  </si>
-  <si>
-    <t>Condición de pago</t>
-  </si>
-  <si>
-    <t>TELÉFONO:</t>
-  </si>
-  <si>
-    <t>04124381354</t>
-  </si>
-  <si>
-    <t>5 dias</t>
-  </si>
-  <si>
-    <t>efectivo</t>
-  </si>
-  <si>
-    <t>Ciudad Bolivar</t>
-  </si>
-  <si>
-    <t>Persona de Cont:</t>
-  </si>
-  <si>
-    <t>Nº Directo:</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN:</t>
-  </si>
-  <si>
-    <t>jose</t>
-  </si>
-  <si>
-    <t>ATENCIÓN:</t>
-  </si>
-  <si>
     <t>Nro de Cotización:</t>
   </si>
   <si>
     <t>E-MAIL:</t>
   </si>
   <si>
-    <t>jose@gmail.com</t>
+    <t>bodega@gmail.com</t>
   </si>
   <si>
     <t>Estimados señores:</t>
@@ -121,19 +124,13 @@
     <t>UND</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>Bloque cemento 15cm</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>TOTAL MONTO</t>
   </si>
   <si>
-    <t>100</t>
+    <t>KG</t>
   </si>
   <si>
     <t>Electrodo 6013</t>
@@ -1051,11 +1048,11 @@
       <c r="H3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="12">
+        <v>46087</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>9</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
@@ -1071,10 +1068,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="4"/>
       <c r="H4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>11</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
@@ -1084,43 +1081,43 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
       <c r="H5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>14</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" ht="9.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>17</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="16"/>
@@ -1129,10 +1126,10 @@
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>20</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" ht="7.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1152,7 +1149,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1171,7 +1168,7 @@
       <c r="F10" s="27"/>
       <c r="G10" s="4"/>
       <c r="H10" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>7</v>
@@ -1179,11 +1176,11 @@
     </row>
     <row r="11" ht="12.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="31"/>
@@ -1205,7 +1202,7 @@
     </row>
     <row r="13" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="33"/>
@@ -1219,7 +1216,7 @@
     </row>
     <row r="14" ht="26.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="33"/>
       <c r="C14" s="33"/>
@@ -1254,22 +1251,22 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="39"/>
       <c r="H17" s="36"/>
@@ -1281,22 +1278,22 @@
         <v>1</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="42" t="s">
         <v>34</v>
+      </c>
+      <c r="C18" s="42">
+        <v>50</v>
       </c>
       <c r="D18" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="42">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="42">
+        <v>75</v>
+      </c>
+      <c r="H18" s="43" t="s">
         <v>36</v>
-      </c>
-      <c r="F18" s="42">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>37</v>
       </c>
       <c r="I18" s="43"/>
     </row>
@@ -1305,22 +1302,22 @@
         <v>2</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="42">
+        <v>2</v>
+      </c>
+      <c r="D19" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>36</v>
+      <c r="E19" s="42">
+        <v>40</v>
       </c>
       <c r="F19" s="42">
-        <v>2000</v>
+        <v>80</v>
       </c>
       <c r="H19" s="44">
-        <v>3000</v>
+        <v>155</v>
       </c>
       <c r="I19" s="44"/>
     </row>
